--- a/Heatmaps pathway detection.xlsx
+++ b/Heatmaps pathway detection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infer\Desktop\R-Work\pathway-analysis-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{338B05A3-79F2-4AC5-9C55-0836B13207F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F41D2B-C7DB-48D7-ACA5-C7822889178C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7770" xr2:uid="{54EA77A7-AB81-4A5F-B959-7CAAD8AD28DF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="5715" windowHeight="7770" xr2:uid="{54EA77A7-AB81-4A5F-B959-7CAAD8AD28DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,16 +72,16 @@
     <t>If correct pathway has FDR &lt; 0.05</t>
   </si>
   <si>
-    <t>If FDR of correct pathway is the lowest as well as significant</t>
-  </si>
-  <si>
     <t>If FDR of correct pathway is the lowest but not necessarily significant</t>
   </si>
   <si>
     <t>Number of significant pathways detected by MetaboAnalyst</t>
   </si>
   <si>
-    <t>If correct pathway ranks in the top 5, when ranked by lowest FDR, and is significant</t>
+    <t>If FDR of correct pathway is the lowest as well as FDR &lt; 0.05</t>
+  </si>
+  <si>
+    <t>If correct pathway ranks in the top 5, when ranking by FDR, and FDR &lt; 0.05</t>
   </si>
 </sst>
 </file>
@@ -127,7 +127,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,12 +448,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -660,8 +666,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -870,8 +881,14 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
@@ -1082,6 +1099,13 @@
       <c r="A31" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
@@ -1290,8 +1314,13 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
@@ -1499,6 +1528,13 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3:H9 B13:H19 B23:H29 B33:H39">
     <cfRule type="colorScale" priority="2">
       <colorScale>
